--- a/src/views/order/order_template.xlsx
+++ b/src/views/order/order_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,39 +29,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>姓名</t>
-  </si>
-  <si>
-    <t>电话</t>
-  </si>
-  <si>
-    <t>身份证</t>
-  </si>
-  <si>
-    <t>省</t>
-  </si>
-  <si>
-    <t>省编码</t>
-  </si>
-  <si>
-    <t>市</t>
-  </si>
-  <si>
-    <t>市编码</t>
-  </si>
-  <si>
-    <t>区</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+  <si>
+    <t>收货人</t>
+  </si>
+  <si>
+    <t>收货人手机号</t>
+  </si>
+  <si>
+    <t>收货人身份证</t>
+  </si>
+  <si>
+    <t>省份名称</t>
+  </si>
+  <si>
+    <t>省份编码</t>
+  </si>
+  <si>
+    <t>城市名称</t>
+  </si>
+  <si>
+    <t>城市编码</t>
+  </si>
+  <si>
+    <t>区名称</t>
   </si>
   <si>
     <t>区编码</t>
   </si>
   <si>
-    <t>地址</t>
+    <t>收货地址</t>
+  </si>
+  <si>
+    <t>预选手机号</t>
   </si>
   <si>
     <t>商品编码</t>
+  </si>
+  <si>
+    <r>
+      <t>张三</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（必填）</t>
+    </r>
+  </si>
+  <si>
+    <t>13058122954（必填）</t>
+  </si>
+  <si>
+    <t>421023199212162436（必填）</t>
+  </si>
+  <si>
+    <t>xx省（必填）</t>
+  </si>
+  <si>
+    <t>（非必填）</t>
+  </si>
+  <si>
+    <t>xx市（必填）</t>
+  </si>
+  <si>
+    <t>xx区（必填）</t>
+  </si>
+  <si>
+    <t>xxx小区xx栋（必填）</t>
+  </si>
+  <si>
+    <t>gzdx-29-80g-qc100（必填）</t>
   </si>
 </sst>
 </file>
@@ -74,10 +116,25 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -236,7 +293,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="4" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,144 +610,150 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1004,13 +1067,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="11" width="9" style="1"/>
+    <col min="1" max="2" width="15.6363636363636" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.4545454545455" style="1" customWidth="1"/>
+    <col min="4" max="9" width="15.6363636363636" style="1" customWidth="1"/>
+    <col min="10" max="10" width="56.0909090909091" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="24.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:11">
+    <row r="1" ht="26" customHeight="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1043,6 +1111,47 @@
       </c>
       <c r="K1" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1056,7 +1165,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1068,7 +1177,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
